--- a/指导书工作台/tests/fixtures/合成老格式样本.xlsx
+++ b/指导书工作台/tests/fixtures/合成老格式样本.xlsx
@@ -1,38 +1,38 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="759" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="清单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="1可选项" sheetId="3" state="hidden" r:id="rId3"/>
-    <sheet name="附件1" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="2" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="附件2" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="3交替动作" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="3-1" sheetId="8" state="hidden" r:id="rId8"/>
-    <sheet name="附件3" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="4" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="4-1瞬间动作" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="4-1" sheetId="12" state="hidden" r:id="rId12"/>
-    <sheet name="附件4-1" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="5" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="5-1" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="5-2" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="6" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="6-1" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="6-2" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="6附件" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="7" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="8" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="9." sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="10" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="11" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="12" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="13" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="清单" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1可选项" sheetId="3" state="hidden" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件1" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件2" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3交替动作" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3-1" sheetId="8" state="hidden" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件3" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-1瞬间动作" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4-1" sheetId="12" state="hidden" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="附件4-1" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-1" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5-2" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-1" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6-2" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6附件" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9." sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13" sheetId="27" state="visible" r:id="rId27"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'清单'!$A$1:$I$40</definedName>
@@ -5715,7 +5715,7 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -5733,26 +5733,26 @@
       <nvPicPr>
         <cNvPr id="11" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect l="16107" t="1176" r="17430" b="7759"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="16107" t="1176" r="17430" b="7759"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1713230" y="2143125"/>
           <a:ext cx="618490" cy="827405"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -5777,26 +5777,26 @@
       <nvPicPr>
         <cNvPr id="12" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect l="21204" t="11206" r="21075" b="21301"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="21204" t="11206" r="21075" b="21301"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2123440" y="990600"/>
           <a:ext cx="666750" cy="704215"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -5821,26 +5821,26 @@
       <nvPicPr>
         <cNvPr id="13" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:srcRect l="20619" t="6306" r="12254" b="8988"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="20619" t="6306" r="12254" b="8988"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="314325" y="3895725"/>
           <a:ext cx="1019175" cy="1143000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -5865,25 +5865,25 @@
       <nvPicPr>
         <cNvPr id="14" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3401695" y="4076700"/>
           <a:ext cx="1558925" cy="1343660"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -5908,26 +5908,26 @@
       <nvPicPr>
         <cNvPr id="15" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:srcRect l="6366" t="2561" r="6823" b="4234"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="6366" t="2561" r="6823" b="4234"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5114925" y="4086225"/>
           <a:ext cx="1371600" cy="1314450"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -5952,25 +5952,25 @@
       <nvPicPr>
         <cNvPr id="17" name="图片 9"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="56515" y="1305560"/>
           <a:ext cx="1261110" cy="1022350"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -5995,28 +5995,28 @@
       <nvPicPr>
         <cNvPr id="18" name="图片 10"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
           <lum bright="6000" contrast="6000"/>
         </a:blip>
-        <a:srcRect l="11400" r="13196" b="29095"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="11400" r="13196" b="29095"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1428750" y="3848735"/>
           <a:ext cx="1426845" cy="1344930"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6041,28 +6041,28 @@
       <nvPicPr>
         <cNvPr id="19" name="图片 11"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId8">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
           <lum bright="6000" contrast="6000"/>
         </a:blip>
-        <a:srcRect r="4932" b="9370"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="4932" b="9370"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3857625" y="1190625"/>
           <a:ext cx="1875155" cy="1735455"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6087,26 +6087,26 @@
       <nvPicPr>
         <cNvPr id="20" name="图片 19" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:srcRect r="41885" b="3571"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="41885" b="3571"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="5400000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="5400000">
           <a:off x="2493645" y="2209800"/>
           <a:ext cx="625475" cy="763270"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6118,7 +6118,7 @@
 </file>
 
 <file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -6136,26 +6136,26 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="26913" t="32381" r="24850" b="31429"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="26913" t="32381" r="24850" b="31429"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="133350" y="1313815"/>
           <a:ext cx="1202055" cy="1200785"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6180,28 +6180,28 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 10" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <lum bright="12000" contrast="6000"/>
         </a:blip>
-        <a:srcRect l="9402" t="16602" r="22926" b="20361"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="9402" t="16602" r="22926" b="20361"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1609725" y="1448435"/>
           <a:ext cx="1538605" cy="1066165"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6226,24 +6226,24 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="981075" y="3585845"/>
           <a:ext cx="1243965" cy="1814830"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6267,28 +6267,28 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 24" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <lum bright="6000" contrast="6000"/>
         </a:blip>
-        <a:srcRect/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5095875" y="1150620"/>
           <a:ext cx="1619250" cy="1802130"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6313,24 +6313,24 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3409950" y="1139825"/>
           <a:ext cx="1501775" cy="672465"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6341,7 +6341,7 @@
 </file>
 
 <file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -6359,26 +6359,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 1" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="76200" y="942975"/>
           <a:ext cx="1676400" cy="1370965"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6403,26 +6403,26 @@
       <nvPicPr>
         <cNvPr id="3" name="Picture 18" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1752600" y="952500"/>
           <a:ext cx="1809750" cy="1362075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6447,26 +6447,26 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4391025" y="962025"/>
           <a:ext cx="1476375" cy="1519555"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6491,24 +6491,24 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4291965" y="3581400"/>
           <a:ext cx="1503045" cy="1722120"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -6532,26 +6532,26 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:srcRect l="6334" t="20929" r="2007"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="6334" t="20929" r="2007"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="714375" y="3438525"/>
           <a:ext cx="2132330" cy="1697355"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6563,7 +6563,7 @@
 </file>
 
 <file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -6581,26 +6581,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 1" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="76200" y="942975"/>
           <a:ext cx="1676400" cy="1370965"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6625,26 +6625,26 @@
       <nvPicPr>
         <cNvPr id="3" name="Picture 18" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1924050" y="1190625"/>
           <a:ext cx="1371600" cy="1032510"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6669,25 +6669,25 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="534035" y="3743325"/>
           <a:ext cx="2184400" cy="1397635"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6712,25 +6712,25 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4467225" y="3695700"/>
           <a:ext cx="1647825" cy="1478915"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6742,7 +6742,7 @@
 </file>
 
 <file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -6760,26 +6760,26 @@
       <nvPicPr>
         <cNvPr id="2" name="Picture 1" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="76200" y="942975"/>
           <a:ext cx="1676400" cy="1370965"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6804,26 +6804,26 @@
       <nvPicPr>
         <cNvPr id="3" name="Picture 18" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1924050" y="1190625"/>
           <a:ext cx="1371600" cy="1032510"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6848,26 +6848,26 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:srcRect l="11670" t="56935" r="73039" b="20700"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="11670" t="56935" r="73039" b="20700"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4391025" y="1123950"/>
           <a:ext cx="1650365" cy="1229360"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6892,25 +6892,25 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4200525" y="3771900"/>
           <a:ext cx="1927860" cy="1438275"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6935,25 +6935,25 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="990600" y="3505200"/>
           <a:ext cx="1322070" cy="1695450"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -6965,7 +6965,7 @@
 </file>
 
 <file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -6983,24 +6983,24 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="721360" y="981075"/>
           <a:ext cx="1355090" cy="1994535"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7024,25 +7024,25 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="628650" y="3514725"/>
           <a:ext cx="2142490" cy="2066925"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7067,27 +7067,27 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <lum bright="6000" contrast="6000"/>
         </a:blip>
-        <a:stretch>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3966845" y="887095"/>
           <a:ext cx="1877060" cy="2315210"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7099,7 +7099,7 @@
 </file>
 
 <file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -7117,24 +7117,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="721360" y="981075"/>
           <a:ext cx="1355090" cy="1994535"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7158,25 +7158,25 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="714375" y="3495675"/>
           <a:ext cx="1737995" cy="2058035"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7201,28 +7201,28 @@
       <nvPicPr>
         <cNvPr id="8" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3">
           <lum bright="6000" contrast="6000"/>
         </a:blip>
-        <a:srcRect t="1579" r="-937"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" t="1579" r="-937"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3971925" y="866775"/>
           <a:ext cx="1438275" cy="2270125"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7234,7 +7234,7 @@
 </file>
 
 <file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -7252,24 +7252,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="721360" y="981075"/>
           <a:ext cx="1355090" cy="1994535"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7293,25 +7293,25 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3981450" y="866775"/>
           <a:ext cx="1495425" cy="2381885"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7336,25 +7336,25 @@
       <nvPicPr>
         <cNvPr id="8" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="904875" y="3543300"/>
           <a:ext cx="1425575" cy="1905000"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7366,7 +7366,7 @@
 </file>
 
 <file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -7384,26 +7384,26 @@
       <nvPicPr>
         <cNvPr id="160" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="895350" y="1495425"/>
           <a:ext cx="2571750" cy="1543050"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7428,26 +7428,26 @@
       <nvPicPr>
         <cNvPr id="161" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="828675" y="2868839"/>
           <a:ext cx="2661557" cy="1162957"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7472,26 +7472,26 @@
       <nvPicPr>
         <cNvPr id="165" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:srcRect t="18382" r="7574" b="14275"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" t="18382" r="7574" b="14275"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4800600" y="1733550"/>
           <a:ext cx="2581275" cy="1371600"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7516,26 +7516,26 @@
       <nvPicPr>
         <cNvPr id="167" name="Picture 10" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:srcRect l="15430" r="24707" b="4861"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="15430" r="24707" b="4861"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr bwMode="auto">
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5133975" y="4067175"/>
           <a:ext cx="1666875" cy="1819275"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7560,24 +7560,24 @@
       <nvPicPr>
         <cNvPr id="171" name="图片 170"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="752475" y="4857750"/>
           <a:ext cx="2486025" cy="2249261"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7588,7 +7588,7 @@
 </file>
 
 <file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -7606,24 +7606,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="438150" y="933450"/>
           <a:ext cx="2228850" cy="1095375"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7647,24 +7647,24 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="419100" y="2076450"/>
           <a:ext cx="2247900" cy="824865"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7688,24 +7688,24 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="256540" y="7103745"/>
           <a:ext cx="1487170" cy="1417955"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7729,24 +7729,24 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1971675" y="6905625"/>
           <a:ext cx="1647825" cy="1857375"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7770,26 +7770,26 @@
       <nvPicPr>
         <cNvPr id="13" name="Picture 10" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId5"/>
-        <a:srcRect l="15430" r="24707" b="4861"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="15430" r="24707" b="4861"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4276090" y="3963035"/>
           <a:ext cx="1590675" cy="1524635"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7814,25 +7814,25 @@
       <nvPicPr>
         <cNvPr id="14" name="图片 13"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="495935" y="3619500"/>
           <a:ext cx="1799590" cy="1714500"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7857,26 +7857,26 @@
       <nvPicPr>
         <cNvPr id="15" name="图片 14"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:srcRect t="6747" r="3090"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" t="6747" r="3090"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4314825" y="809625"/>
           <a:ext cx="1456690" cy="2001520"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -7888,7 +7888,7 @@
 </file>
 
 <file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -7906,24 +7906,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="238125" y="923925"/>
           <a:ext cx="2466975" cy="1057275"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7947,24 +7947,24 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="228600" y="2018665"/>
           <a:ext cx="2476500" cy="1030605"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -7988,26 +7988,26 @@
       <nvPicPr>
         <cNvPr id="4" name="Picture 4" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:srcRect l="2" t="41" b="-5989"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="2" t="41" b="-5989"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="400050" y="3505200"/>
           <a:ext cx="2209800" cy="1113790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cap="rnd">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="rnd">
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
@@ -8037,28 +8037,28 @@
       <nvPicPr>
         <cNvPr id="5" name="Picture 5" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <lum bright="12000" contrast="0"/>
         </a:blip>
-        <a:srcRect/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="380365" y="4652645"/>
           <a:ext cx="2245995" cy="970280"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525" cap="rnd">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525" cap="rnd">
           <a:solidFill>
             <a:srgbClr val="000000"/>
           </a:solidFill>
@@ -8088,24 +8088,24 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3723640" y="828040"/>
           <a:ext cx="2077085" cy="1049655"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8129,24 +8129,24 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3152775" y="1952625"/>
           <a:ext cx="1571625" cy="1181735"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8170,24 +8170,24 @@
       <nvPicPr>
         <cNvPr id="8" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4876165" y="1962150"/>
           <a:ext cx="1476375" cy="1177290"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8198,7 +8198,7 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -8216,25 +8216,25 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId1"/>
-        <a:srcRect l="33179" t="40568" r="35002" b="32888"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="33179" t="40568" r="35002" b="32888"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="419100" y="1113790"/>
           <a:ext cx="989965" cy="876935"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8258,26 +8258,26 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="294640" y="2416810"/>
           <a:ext cx="1048385" cy="359410"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8302,24 +8302,24 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2009775" y="1111250"/>
           <a:ext cx="952500" cy="874395"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8343,24 +8343,24 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="9525" y="3931285"/>
           <a:ext cx="1377950" cy="1249680"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8384,24 +8384,24 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1875790" y="3933190"/>
           <a:ext cx="1256030" cy="1190625"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8425,25 +8425,25 @@
       <nvPicPr>
         <cNvPr id="8" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:srcRect l="30179" t="32450" r="20097" b="34437"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="30179" t="32450" r="20097" b="34437"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4152900" y="1095375"/>
           <a:ext cx="1727200" cy="1533525"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8467,24 +8467,24 @@
       <nvPicPr>
         <cNvPr id="9" name="图片 8"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4218940" y="3750945"/>
           <a:ext cx="1486535" cy="1367155"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8508,26 +8508,26 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 3" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:srcRect r="41885" b="3571"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="41885" b="3571"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="5400000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="5400000">
           <a:off x="2098040" y="2204720"/>
           <a:ext cx="720725" cy="879475"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8539,7 +8539,7 @@
 </file>
 
 <file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -8557,24 +8557,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="552450" y="962025"/>
           <a:ext cx="1647825" cy="2130425"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8598,26 +8598,26 @@
       <nvPicPr>
         <cNvPr id="6" name="Picture 10" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:srcRect l="15430" r="24707" b="4861"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="15430" r="24707" b="4861"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4095750" y="933450"/>
           <a:ext cx="1619250" cy="1552575"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8642,25 +8642,25 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="866775" y="3409950"/>
           <a:ext cx="1534160" cy="2087880"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8672,7 +8672,7 @@
 </file>
 
 <file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -8690,25 +8690,25 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="104775" y="1028700"/>
           <a:ext cx="2700020" cy="1759585"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8733,25 +8733,25 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3363595" y="1035050"/>
           <a:ext cx="2470785" cy="1995805"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8776,25 +8776,25 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="113030" y="3319145"/>
           <a:ext cx="2498725" cy="1857375"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8806,7 +8806,7 @@
 </file>
 
 <file path=xl/drawings/drawing22.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -8824,24 +8824,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="504825" y="1076325"/>
           <a:ext cx="1577975" cy="1807210"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -8865,25 +8865,25 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3381375" y="1028700"/>
           <a:ext cx="2766695" cy="1335405"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8908,25 +8908,25 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3714750" y="2352675"/>
           <a:ext cx="1915160" cy="1464945"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8951,25 +8951,25 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="5400000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="5400000">
           <a:off x="4104640" y="4100195"/>
           <a:ext cx="1443355" cy="1885950"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -8981,7 +8981,7 @@
 </file>
 
 <file path=xl/drawings/drawing23.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>2</col>
@@ -8999,25 +8999,25 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4024630" y="4424680"/>
           <a:ext cx="1104265" cy="1055370"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9042,27 +9042,27 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <lum bright="17996" contrast="11998"/>
         </a:blip>
-        <a:stretch>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3304540" y="1130935"/>
           <a:ext cx="1119505" cy="890270"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9087,25 +9087,25 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1709420" y="4953000"/>
           <a:ext cx="1463675" cy="563880"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9130,25 +9130,25 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="9525" y="3729355"/>
           <a:ext cx="1630680" cy="646430"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9173,25 +9173,25 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="180975" y="4932680"/>
           <a:ext cx="1107440" cy="473710"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9216,25 +9216,25 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1782445" y="3649345"/>
           <a:ext cx="1314450" cy="770890"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9259,25 +9259,25 @@
       <nvPicPr>
         <cNvPr id="8" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1219200" y="2434590"/>
           <a:ext cx="1593850" cy="593090"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9302,25 +9302,25 @@
       <nvPicPr>
         <cNvPr id="9" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="371475" y="1137285"/>
           <a:ext cx="1539240" cy="603885"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9345,28 +9345,28 @@
       <nvPicPr>
         <cNvPr id="10" name="Picture 37085"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId9">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
           <lum bright="19995" contrast="0"/>
         </a:blip>
-        <a:srcRect l="1511" t="7074" r="4330" b="2654"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="1511" t="7074" r="4330" b="2654"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5715" y="2298700"/>
           <a:ext cx="1054735" cy="778510"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="1">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="1">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9391,25 +9391,25 @@
       <nvPicPr>
         <cNvPr id="11" name="图片 9"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4043045" y="2486660"/>
           <a:ext cx="1097280" cy="1311910"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9421,7 +9421,7 @@
 </file>
 
 <file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -9439,24 +9439,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="10800000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="10800000">
           <a:off x="1352550" y="1114425"/>
           <a:ext cx="953770" cy="876300"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9480,25 +9480,25 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId2"/>
-        <a:srcRect l="43366" t="48757" r="44350" b="40795"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="43366" t="48757" r="44350" b="40795"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="571500" y="1400175"/>
           <a:ext cx="390525" cy="352425"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9522,25 +9522,25 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="10229850" y="1314450"/>
           <a:ext cx="1527175" cy="1342390"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9565,26 +9565,26 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:srcRect r="41885" b="3571"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" r="41885" b="3571"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2962275" y="923925"/>
           <a:ext cx="957580" cy="1165225"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -9596,7 +9596,7 @@
 </file>
 
 <file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -9614,24 +9614,24 @@
       <nvPicPr>
         <cNvPr id="12" name="图片 11"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="16200000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="16200000">
           <a:off x="318770" y="880745"/>
           <a:ext cx="1071880" cy="1414145"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9655,24 +9655,24 @@
       <nvPicPr>
         <cNvPr id="13" name="图片 12"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1676400" y="1052830"/>
           <a:ext cx="1571625" cy="1080770"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9696,24 +9696,24 @@
       <nvPicPr>
         <cNvPr id="14" name="图片 13"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="171450" y="2343150"/>
           <a:ext cx="1295400" cy="1049020"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9737,24 +9737,24 @@
       <nvPicPr>
         <cNvPr id="15" name="图片 14"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1856740" y="2352675"/>
           <a:ext cx="1207135" cy="1038225"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9778,24 +9778,24 @@
       <nvPicPr>
         <cNvPr id="16" name="图片 15"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="158115" y="4194175"/>
           <a:ext cx="1499235" cy="1063625"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9819,25 +9819,25 @@
       <nvPicPr>
         <cNvPr id="17" name="图片 16"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId6"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1809750" y="3983355"/>
           <a:ext cx="1076325" cy="1435735"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9861,24 +9861,24 @@
       <nvPicPr>
         <cNvPr id="18" name="图片 17"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3437890" y="1018540"/>
           <a:ext cx="1562735" cy="1543050"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9902,24 +9902,24 @@
       <nvPicPr>
         <cNvPr id="19" name="图片 18"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5092700" y="1018540"/>
           <a:ext cx="1660525" cy="1543685"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9943,24 +9943,24 @@
       <nvPicPr>
         <cNvPr id="20" name="图片 19"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3429000" y="2785745"/>
           <a:ext cx="1552575" cy="1207770"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -9984,24 +9984,24 @@
       <nvPicPr>
         <cNvPr id="21" name="图片 20"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5133975" y="2771775"/>
           <a:ext cx="1619250" cy="1235075"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10025,24 +10025,24 @@
       <nvPicPr>
         <cNvPr id="22" name="图片 21"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="16200000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="16200000">
           <a:off x="3618865" y="3933825"/>
           <a:ext cx="1362075" cy="1875790"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10066,24 +10066,24 @@
       <nvPicPr>
         <cNvPr id="24" name="图片 23"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5895975" y="4489450"/>
           <a:ext cx="895350" cy="406400"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10094,7 +10094,7 @@
 </file>
 
 <file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -10112,24 +10112,24 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="16200000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="16200000">
           <a:off x="1062355" y="803910"/>
           <a:ext cx="1047750" cy="1382395"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10140,7 +10140,7 @@
 </file>
 
 <file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -10158,24 +10158,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="285750" y="923290"/>
           <a:ext cx="1304925" cy="1078230"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10199,24 +10199,24 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1952625" y="923925"/>
           <a:ext cx="1276350" cy="1076325"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10240,24 +10240,24 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="295275" y="2162175"/>
           <a:ext cx="1097915" cy="904875"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10281,24 +10281,24 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="16200000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="16200000">
           <a:off x="2138045" y="1973580"/>
           <a:ext cx="930910" cy="1307465"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10322,24 +10322,24 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="384810" y="3533140"/>
           <a:ext cx="958215" cy="1831975"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10363,24 +10363,24 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2562225" y="3524250"/>
           <a:ext cx="1095375" cy="1838325"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10404,24 +10404,24 @@
       <nvPicPr>
         <cNvPr id="8" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4086225" y="933450"/>
           <a:ext cx="1028065" cy="1982470"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10445,24 +10445,24 @@
       <nvPicPr>
         <cNvPr id="9" name="图片 8"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="6168390" y="933450"/>
           <a:ext cx="1156335" cy="1849755"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10486,24 +10486,24 @@
       <nvPicPr>
         <cNvPr id="10" name="图片 9"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3952240" y="3838575"/>
           <a:ext cx="1353820" cy="1085850"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10527,24 +10527,24 @@
       <nvPicPr>
         <cNvPr id="11" name="图片 10"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5705475" y="3409950"/>
           <a:ext cx="1104265" cy="1837690"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10568,24 +10568,24 @@
       <nvPicPr>
         <cNvPr id="13" name="图片 12"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5819775" y="1019175"/>
           <a:ext cx="300355" cy="304800"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10609,24 +10609,24 @@
       <nvPicPr>
         <cNvPr id="15" name="图片 14"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="16200000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="16200000">
           <a:off x="2273935" y="3554730"/>
           <a:ext cx="225425" cy="278130"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10637,7 +10637,7 @@
 </file>
 
 <file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -10655,24 +10655,24 @@
       <nvPicPr>
         <cNvPr id="16" name="图片 15"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2722245" y="1654175"/>
           <a:ext cx="1406525" cy="1441450"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10696,24 +10696,24 @@
       <nvPicPr>
         <cNvPr id="17" name="图片 16"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="279400" y="1662430"/>
           <a:ext cx="1793875" cy="1433195"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10737,25 +10737,25 @@
       <nvPicPr>
         <cNvPr id="18" name="图片 17"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId3"/>
-        <a:srcRect l="33179" t="40568" r="35002" b="32888"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="33179" t="40568" r="35002" b="32888"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="307340" y="3606800"/>
           <a:ext cx="1365885" cy="1188720"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10779,26 +10779,26 @@
       <nvPicPr>
         <cNvPr id="19" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2824480" y="3579495"/>
           <a:ext cx="1315720" cy="1216025"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -10823,24 +10823,24 @@
       <nvPicPr>
         <cNvPr id="20" name="图片 19"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="497205" y="6520815"/>
           <a:ext cx="1628775" cy="1457960"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10864,24 +10864,24 @@
       <nvPicPr>
         <cNvPr id="21" name="图片 20"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2849880" y="6503035"/>
           <a:ext cx="1548765" cy="1449070"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10905,24 +10905,24 @@
       <nvPicPr>
         <cNvPr id="22" name="图片 21"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2874645" y="8018780"/>
           <a:ext cx="1487805" cy="1346200"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10946,25 +10946,25 @@
       <nvPicPr>
         <cNvPr id="24" name="图片 23"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip cstate="print" r:embed="rId8"/>
-        <a:srcRect l="30179" t="32450" r="20097" b="34437"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="30179" t="32450" r="20097" b="34437"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="457200" y="8018780"/>
           <a:ext cx="1511300" cy="1319530"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -10988,24 +10988,24 @@
       <nvPicPr>
         <cNvPr id="25" name="图片 24"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId9"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4822825" y="1692275"/>
           <a:ext cx="1886585" cy="2401570"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11029,24 +11029,24 @@
       <nvPicPr>
         <cNvPr id="26" name="图片 25"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="7134225" y="1946910"/>
           <a:ext cx="1946275" cy="1659890"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11070,26 +11070,26 @@
       <nvPicPr>
         <cNvPr id="27" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId11"/>
-        <a:srcRect/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="7417435" y="5395595"/>
           <a:ext cx="1501140" cy="1402715"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11114,26 +11114,26 @@
       <nvPicPr>
         <cNvPr id="28" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1" noChangeArrowheads="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1" noChangeArrowheads="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId12"/>
-        <a:srcRect l="26913" t="32381" r="24850" b="31429"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="26913" t="32381" r="24850" b="31429"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="6099175" y="7037070"/>
           <a:ext cx="1929765" cy="1885315"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln>
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11158,24 +11158,24 @@
       <nvPicPr>
         <cNvPr id="29" name="图片 28"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId13"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5254625" y="5375275"/>
           <a:ext cx="1669415" cy="1421765"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11186,7 +11186,7 @@
 </file>
 
 <file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>1</col>
@@ -11204,24 +11204,24 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 1"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1828800" y="1000125"/>
           <a:ext cx="895350" cy="913765"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11245,24 +11245,24 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 2"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="104140" y="2094865"/>
           <a:ext cx="1269365" cy="1021080"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11286,24 +11286,24 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 3"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="16200000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="16200000">
           <a:off x="434975" y="856615"/>
           <a:ext cx="867410" cy="1198245"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11327,24 +11327,24 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 4"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="133350" y="3590925"/>
           <a:ext cx="1409700" cy="1604645"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11368,24 +11368,24 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 5"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="1543050" y="3886200"/>
           <a:ext cx="1571625" cy="1230630"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11409,24 +11409,24 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 6"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3943350" y="1113790"/>
           <a:ext cx="1430655" cy="2086610"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11450,24 +11450,24 @@
       <nvPicPr>
         <cNvPr id="8" name="图片 7"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4705985" y="3429000"/>
           <a:ext cx="1618615" cy="1676400"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11491,24 +11491,24 @@
       <nvPicPr>
         <cNvPr id="9" name="图片 8"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId8"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="3267075" y="3895725"/>
           <a:ext cx="1369695" cy="612775"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:ln>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:prstDash val="solid"/>
         </a:ln>
       </spPr>
@@ -11519,7 +11519,7 @@
 </file>
 
 <file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <twoCellAnchor editAs="oneCell">
     <from>
       <col>0</col>
@@ -11537,28 +11537,28 @@
       <nvPicPr>
         <cNvPr id="2" name="图片 2" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId1">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
           <lum bright="12000" contrast="6000"/>
         </a:blip>
-        <a:srcRect l="9402" t="16602" r="22926" b="20361"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="9402" t="16602" r="22926" b="20361"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="200660" y="1621790"/>
           <a:ext cx="1786890" cy="1258570"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11583,28 +11583,28 @@
       <nvPicPr>
         <cNvPr id="3" name="图片 13" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId2">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
           <lum bright="17999" contrast="0"/>
         </a:blip>
-        <a:srcRect l="55341" t="26642" r="17647" b="43217"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="55341" t="26642" r="17647" b="43217"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2755900" y="3409950"/>
           <a:ext cx="1123315" cy="942975"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11629,25 +11629,25 @@
       <nvPicPr>
         <cNvPr id="4" name="图片 18" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId3"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2509520" y="1407160"/>
           <a:ext cx="1381125" cy="1442085"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11672,28 +11672,28 @@
       <nvPicPr>
         <cNvPr id="5" name="图片 19" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId4">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4">
           <lum bright="12000" contrast="6000"/>
         </a:blip>
-        <a:srcRect l="76149" t="35963" r="6799" b="41757"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="76149" t="35963" r="6799" b="41757"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="513715" y="3308350"/>
           <a:ext cx="1154430" cy="1134110"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11718,26 +11718,26 @@
       <nvPicPr>
         <cNvPr id="6" name="图片 20" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId5"/>
-        <a:srcRect l="14076" t="27979" r="47118" b="36067"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="14076" t="27979" r="47118" b="36067"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="4575175" y="1681480"/>
           <a:ext cx="1918970" cy="1337310"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11762,28 +11762,28 @@
       <nvPicPr>
         <cNvPr id="7" name="图片 22" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId6">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6">
           <lum bright="6000" contrast="6000"/>
         </a:blip>
-        <a:srcRect l="17343" t="21999" r="32451" b="33488"/>
-        <a:stretch>
+        <a:srcRect xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" l="17343" t="21999" r="32451" b="33488"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="6526530" y="1628775"/>
           <a:ext cx="2130425" cy="1420495"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11808,27 +11808,27 @@
       <nvPicPr>
         <cNvPr id="8" name="图片 23" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId7">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7">
           <lum bright="12000" contrast="0"/>
         </a:blip>
-        <a:stretch>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm rot="-5400000">
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" rot="-5400000">
           <a:off x="5770245" y="3542665"/>
           <a:ext cx="1683385" cy="1958340"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11853,27 +11853,27 @@
       <nvPicPr>
         <cNvPr id="9" name="图片 24" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId8">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8">
           <lum bright="6000" contrast="6000"/>
         </a:blip>
-        <a:stretch>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="5503545" y="6038215"/>
           <a:ext cx="2348230" cy="2489200"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11898,27 +11898,27 @@
       <nvPicPr>
         <cNvPr id="10" name="图片 25" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId9">
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9">
           <lum bright="12000" contrast="6000"/>
         </a:blip>
-        <a:stretch>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="2018030" y="5640070"/>
           <a:ext cx="1667510" cy="1724660"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -11943,25 +11943,25 @@
       <nvPicPr>
         <cNvPr id="11" name="图片 27" descr="占位图"/>
         <cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+          <a:picLocks xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" noChangeAspect="1"/>
         </cNvPicPr>
       </nvPicPr>
       <blipFill>
-        <a:blip r:embed="rId10"/>
-        <a:stretch>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
       </blipFill>
       <spPr>
-        <a:xfrm>
+        <a:xfrm xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:off x="347345" y="5661660"/>
           <a:ext cx="1616710" cy="1687830"/>
         </a:xfrm>
-        <a:prstGeom prst="rect">
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect">
           <avLst/>
         </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
+        <a:noFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="9525">
           <a:noFill/>
           <a:prstDash val="solid"/>
         </a:ln>
@@ -14055,7 +14055,7 @@
       <c r="H7" s="1099" t="n"/>
       <c r="I7" s="253" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -22393,7 +22393,7 @@
       <c r="H7" s="1132" t="n"/>
       <c r="I7" s="483" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -31519,7 +31519,7 @@
       <c r="H7" s="1035" t="n"/>
       <c r="I7" s="128" t="inlineStr">
         <is>
-          <t> </t>
+          <t xml:space="preserve"> </t>
         </is>
       </c>
     </row>
@@ -31903,7 +31903,7 @@
       <c r="H30" s="664" t="n"/>
       <c r="K30" s="128" t="inlineStr">
         <is>
-          <t>                                                                          </t>
+          <t xml:space="preserve">                                                                          </t>
         </is>
       </c>
     </row>
@@ -31928,7 +31928,7 @@
       <c r="H32" s="664" t="n"/>
       <c r="K32" s="128" t="inlineStr">
         <is>
-          <t>                                                                          </t>
+          <t xml:space="preserve">                                                                          </t>
         </is>
       </c>
     </row>
